--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487000_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487000_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>O. THIAM PEDRERA</t>
+          <t>A. SMITH</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.3156</v>
+        <v>1.16</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8367</v>
+        <v>3.3628</v>
       </c>
       <c r="F2" t="n">
-        <v>0.479</v>
+        <v>-2.2028</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.505</v>
+        <v>0.8419</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.7685999999999999</v>
+        <v>1.2783</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.7364000000000001</v>
+        <v>-0.4364</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2699</v>
+        <v>3.6062</v>
       </c>
       <c r="K2" t="n">
-        <v>0.7305</v>
+        <v>2.3038</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.4606</v>
+        <v>1.3024</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.775</v>
+        <v>-2.7643</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.4991</v>
+        <v>-1.0255</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.2759</v>
+        <v>-1.7388</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.8214</v>
+        <v>0.2053</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.0534</v>
+        <v>-1.0267</v>
       </c>
       <c r="R2" t="n">
         <v>1.2321</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6339</v>
+        <v>-0.7168</v>
       </c>
       <c r="T2" t="n">
-        <v>0.612</v>
+        <v>-0.8757</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0219</v>
+        <v>0.159</v>
       </c>
       <c r="V2" t="n">
-        <v>2.0082</v>
+        <v>0.8295</v>
       </c>
       <c r="W2" t="n">
-        <v>2.0082</v>
+        <v>1.6591</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-0.8295</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. SMITH</t>
+          <t>H. FIGUEROA ÁLVAREZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9368</v>
+        <v>1.0953</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2582</v>
+        <v>2.5571</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.3214</v>
+        <v>-1.4618</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8419</v>
+        <v>-1.7666</v>
       </c>
       <c r="H3" t="n">
-        <v>1.2783</v>
+        <v>-2.5663</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4364</v>
+        <v>0.7997</v>
       </c>
       <c r="J3" t="n">
-        <v>3.6062</v>
+        <v>0.9631999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>2.3038</v>
+        <v>-1.1806</v>
       </c>
       <c r="L3" t="n">
-        <v>1.3024</v>
+        <v>2.1438</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.7643</v>
+        <v>-2.7298</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.0255</v>
+        <v>-1.3857</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.7388</v>
+        <v>-1.3441</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2053</v>
+        <v>0.616</v>
       </c>
       <c r="Q3" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R3" t="n">
-        <v>1.2321</v>
+        <v>1.6427</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9399</v>
+        <v>-0.3516</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9804</v>
+        <v>0.0231</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0404</v>
+        <v>-0.3747</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8295</v>
+        <v>2.5975</v>
       </c>
       <c r="W3" t="n">
-        <v>1.6591</v>
+        <v>2.5975</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.8295</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. FRITZ</t>
+          <t>G. VAZQUEZ VALLEJO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3614</v>
+        <v>0.5261</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3729</v>
+        <v>0.5246</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0115</v>
+        <v>0.0015</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.104</v>
+        <v>-0.6245000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1621</v>
+        <v>-0.4088</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.9418</v>
+        <v>-0.2157</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.615</v>
+        <v>0.5665</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.6939</v>
+        <v>-0.0516</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0789</v>
+        <v>0.6181</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.489</v>
+        <v>-1.191</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5318000000000001</v>
+        <v>-0.3572</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.0208</v>
+        <v>-0.8338</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2053</v>
+        <v>-0.616</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2053</v>
+        <v>1.4374</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7796</v>
+        <v>0.3478</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5075</v>
+        <v>0.3524</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2721</v>
+        <v>-0.0047</v>
       </c>
       <c r="V4" t="n">
-        <v>0.4805</v>
+        <v>1.4189</v>
       </c>
       <c r="W4" t="n">
-        <v>0.4805</v>
+        <v>1.6591</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. VAZQUEZ VALLEJO</t>
+          <t>O. THIAM PEDRERA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0645</v>
+        <v>0.4732</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2735</v>
+        <v>0.3795</v>
       </c>
       <c r="F5" t="n">
-        <v>0.209</v>
+        <v>0.0936</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.6245000000000001</v>
+        <v>-1.505</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.4088</v>
+        <v>-0.7685999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2157</v>
+        <v>-0.7364000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5665</v>
+        <v>0.2699</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.0516</v>
+        <v>0.7305</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6181</v>
+        <v>-0.4606</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.191</v>
+        <v>-1.775</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3572</v>
+        <v>-1.4991</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8338</v>
+        <v>-0.2759</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.616</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q5" t="n">
         <v>-2.0534</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4374</v>
+        <v>1.2321</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2428</v>
+        <v>0.7914</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4457</v>
+        <v>0.1548</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2028</v>
+        <v>0.6366000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>1.4189</v>
+        <v>2.0082</v>
       </c>
       <c r="W5" t="n">
-        <v>1.6591</v>
+        <v>2.0082</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>H. FIGUEROA ÁLVAREZ</t>
+          <t>J. FRITZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1474</v>
+        <v>0.1901</v>
       </c>
       <c r="E6" t="n">
-        <v>1.759</v>
+        <v>0.4388</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.9064</v>
+        <v>-0.2487</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.7666</v>
+        <v>-1.104</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.5663</v>
+        <v>-0.1621</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7997</v>
+        <v>-0.9418</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9631999999999999</v>
+        <v>-0.615</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.1806</v>
+        <v>-0.6939</v>
       </c>
       <c r="L6" t="n">
-        <v>2.1438</v>
+        <v>0.0789</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.7298</v>
+        <v>-0.489</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.3857</v>
+        <v>0.5318000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.3441</v>
+        <v>-1.0208</v>
       </c>
       <c r="P6" t="n">
-        <v>0.616</v>
+        <v>0.2053</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6427</v>
+        <v>0.2053</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.5943</v>
+        <v>0.6083</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.775</v>
+        <v>0.5733</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.8193</v>
+        <v>0.035</v>
       </c>
       <c r="V6" t="n">
-        <v>2.5975</v>
+        <v>0.4805</v>
       </c>
       <c r="W6" t="n">
-        <v>2.5975</v>
+        <v>0.4805</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7302</v>
+        <v>-0.3818</v>
       </c>
       <c r="E7" t="n">
-        <v>0.672</v>
+        <v>0.8425</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.4022</v>
+        <v>-1.2244</v>
       </c>
       <c r="G7" t="n">
         <v>0.7166</v>
@@ -1000,13 +1000,13 @@
         <v>0.8214</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2658</v>
+        <v>0.6141</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5152</v>
+        <v>0.6857</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2494</v>
+        <v>-0.0716</v>
       </c>
       <c r="V7" t="n">
         <v>-0.4805</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3548</v>
+        <v>-2.0151</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.8427</v>
+        <v>-2.6335</v>
       </c>
       <c r="F8" t="n">
-        <v>1.4878</v>
+        <v>0.6183</v>
       </c>
       <c r="G8" t="n">
         <v>-1.0106</v>
@@ -1078,13 +1078,13 @@
         <v>0.616</v>
       </c>
       <c r="S8" t="n">
-        <v>1.4217</v>
+        <v>0.7614</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.651</v>
+        <v>-0.4418</v>
       </c>
       <c r="U8" t="n">
-        <v>2.0727</v>
+        <v>1.2032</v>
       </c>
       <c r="V8" t="n">
         <v>0.6982</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.5115</v>
+        <v>-3.3214</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0891</v>
+        <v>-1.4029</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.4224</v>
+        <v>-1.9185</v>
       </c>
       <c r="G9" t="n">
         <v>-2.1306</v>
@@ -1156,13 +1156,13 @@
         <v>1.2321</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0298</v>
+        <v>0.2199</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2517</v>
+        <v>-0.0621</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2219</v>
+        <v>0.282</v>
       </c>
       <c r="V9" t="n">
         <v>-0.5893</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.8565</v>
+        <v>-4.8879</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.152</v>
+        <v>-1.3612</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.7045</v>
+        <v>-3.5267</v>
       </c>
       <c r="G10" t="n">
         <v>-3.6725</v>
@@ -1234,13 +1234,13 @@
         <v>1.0267</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0054</v>
+        <v>-0.0368</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0541</v>
+        <v>-0.1551</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0595</v>
+        <v>0.1183</v>
       </c>
       <c r="V10" t="n">
         <v>-1.1786</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.8855</v>
+        <v>-6.3963</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1838</v>
+        <v>-3.0207</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.7017</v>
+        <v>-3.3756</v>
       </c>
       <c r="G11" t="n">
         <v>-1.0175</v>
@@ -1312,13 +1312,13 @@
         <v>1.8481</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3373</v>
+        <v>-0.1734</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6778</v>
+        <v>-0.159</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3405</v>
+        <v>-0.0144</v>
       </c>
       <c r="V11" t="n">
         <v>-2.9466</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-13.9366</v>
+        <v>-13.5578</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.6422999999999999</v>
+        <v>-0.3130000000000011</v>
       </c>
       <c r="F12" t="n">
-        <v>-13.2943</v>
+        <v>-13.2451</v>
       </c>
       <c r="G12" t="n">
         <v>-11.2728</v>
@@ -1366,10 +1366,10 @@
         <v>10.0169</v>
       </c>
       <c r="K12" t="n">
-        <v>5.3882</v>
+        <v>5.388199999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>4.628699999999999</v>
+        <v>4.6287</v>
       </c>
       <c r="M12" t="n">
         <v>-21.2899</v>
@@ -1381,7 +1381,7 @@
         <v>-11.587</v>
       </c>
       <c r="P12" t="n">
-        <v>-7.1872</v>
+        <v>-7.187200000000001</v>
       </c>
       <c r="Q12" t="n">
         <v>-18.4806</v>
@@ -1390,16 +1390,16 @@
         <v>11.2939</v>
       </c>
       <c r="S12" t="n">
-        <v>1.6857</v>
+        <v>2.0643</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2338000000000001</v>
+        <v>0.09559999999999982</v>
       </c>
       <c r="U12" t="n">
-        <v>1.9193</v>
+        <v>1.9687</v>
       </c>
       <c r="V12" t="n">
-        <v>2.8378</v>
+        <v>2.837800000000001</v>
       </c>
       <c r="W12" t="n">
         <v>8.055300000000001</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.8078</v>
+        <v>6.5453</v>
       </c>
       <c r="E13" t="n">
-        <v>6.1461</v>
+        <v>6.7737</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3383</v>
+        <v>-0.2285</v>
       </c>
       <c r="G13" t="n">
         <v>5.3463</v>
@@ -1468,13 +1468,13 @@
         <v>1.6427</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.3331</v>
+        <v>-0.5957</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.2516</v>
+        <v>-0.6239</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.08160000000000001</v>
+        <v>0.0283</v>
       </c>
       <c r="V13" t="n">
         <v>1.1786</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>I. ROSA POMPIDO</t>
+          <t>O. RUSSELL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.5156</v>
+        <v>5.3851</v>
       </c>
       <c r="E14" t="n">
-        <v>6.8434</v>
+        <v>2.7472</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.3278</v>
+        <v>2.6379</v>
       </c>
       <c r="G14" t="n">
-        <v>5.6447</v>
+        <v>3.6389</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7299</v>
+        <v>1.4924</v>
       </c>
       <c r="I14" t="n">
-        <v>4.9148</v>
+        <v>2.1465</v>
       </c>
       <c r="J14" t="n">
-        <v>6.828</v>
+        <v>4.1801</v>
       </c>
       <c r="K14" t="n">
-        <v>1.1714</v>
+        <v>2.1286</v>
       </c>
       <c r="L14" t="n">
-        <v>5.6566</v>
+        <v>2.0515</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.1833</v>
+        <v>-0.5411</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.4415</v>
+        <v>-0.6362</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.7418</v>
+        <v>0.095</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2053</v>
+        <v>1.2321</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.0267</v>
+        <v>-2.0534</v>
       </c>
       <c r="R14" t="n">
-        <v>1.2321</v>
+        <v>3.2855</v>
       </c>
       <c r="S14" t="n">
-        <v>0.604</v>
+        <v>-0.4243</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8018999999999999</v>
+        <v>-0.5581</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1979</v>
+        <v>0.1338</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.9384</v>
+        <v>0.9384</v>
       </c>
       <c r="W14" t="n">
-        <v>0.2402</v>
+        <v>1.1786</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.1786</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. BAH</t>
+          <t>I. ROSA POMPIDO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.0981</v>
+        <v>5.2419</v>
       </c>
       <c r="E15" t="n">
-        <v>6.1002</v>
+        <v>6.3204</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.0021</v>
+        <v>-1.0785</v>
       </c>
       <c r="G15" t="n">
-        <v>2.9015</v>
+        <v>5.6447</v>
       </c>
       <c r="H15" t="n">
-        <v>2.3198</v>
+        <v>0.7299</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5816</v>
+        <v>4.9148</v>
       </c>
       <c r="J15" t="n">
-        <v>3.9691</v>
+        <v>6.828</v>
       </c>
       <c r="K15" t="n">
-        <v>3.1798</v>
+        <v>1.1714</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7893</v>
+        <v>5.6566</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.0676</v>
+        <v>-1.1833</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8599</v>
+        <v>-0.4415</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.2077</v>
+        <v>-0.7418</v>
       </c>
       <c r="P15" t="n">
-        <v>1.4374</v>
+        <v>0.2053</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4374</v>
+        <v>1.2321</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.3303</v>
       </c>
       <c r="T15" t="n">
-        <v>1.3016</v>
+        <v>0.2788</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3021</v>
+        <v>0.0514</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.2402</v>
+        <v>-0.9384</v>
       </c>
       <c r="W15" t="n">
-        <v>0.8295</v>
+        <v>0.2402</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0698</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>O. RUSSELL</t>
+          <t>D. BAH</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.3007</v>
+        <v>3.9823</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1196</v>
+        <v>4.845</v>
       </c>
       <c r="F16" t="n">
-        <v>2.1811</v>
+        <v>-0.8626</v>
       </c>
       <c r="G16" t="n">
-        <v>3.6389</v>
+        <v>2.9015</v>
       </c>
       <c r="H16" t="n">
-        <v>1.4924</v>
+        <v>2.3198</v>
       </c>
       <c r="I16" t="n">
-        <v>2.1465</v>
+        <v>0.5816</v>
       </c>
       <c r="J16" t="n">
-        <v>4.1801</v>
+        <v>3.9691</v>
       </c>
       <c r="K16" t="n">
-        <v>2.1286</v>
+        <v>3.1798</v>
       </c>
       <c r="L16" t="n">
-        <v>2.0515</v>
+        <v>0.7893</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.5411</v>
+        <v>-1.0676</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6362</v>
+        <v>-0.8599</v>
       </c>
       <c r="O16" t="n">
-        <v>0.095</v>
+        <v>-0.2077</v>
       </c>
       <c r="P16" t="n">
-        <v>1.2321</v>
+        <v>1.4374</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>3.2855</v>
+        <v>1.4374</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.5087</v>
+        <v>-0.1163</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.1857</v>
+        <v>0.0464</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.323</v>
+        <v>-0.1626</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9384</v>
+        <v>-0.2402</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1786</v>
+        <v>0.8295</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2402</v>
+        <v>-1.0698</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9181</v>
+        <v>1.6556</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.7044</v>
+        <v>-1.0768</v>
       </c>
       <c r="F17" t="n">
-        <v>2.6225</v>
+        <v>2.7323</v>
       </c>
       <c r="G17" t="n">
         <v>-0.9536</v>
@@ -1780,13 +1780,13 @@
         <v>3.2855</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.3254</v>
+        <v>-0.588</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.3833</v>
+        <v>-0.7557</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0579</v>
+        <v>0.1677</v>
       </c>
       <c r="V17" t="n">
         <v>0.9384</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. GARCIA CARRERO</t>
+          <t>R. FABREGA URPINA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9491000000000001</v>
+        <v>-0.7165</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.2002</v>
+        <v>-2.2701</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2511</v>
+        <v>1.5536</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5693</v>
+        <v>0.0187</v>
       </c>
       <c r="H18" t="n">
-        <v>0.72</v>
+        <v>-0.5127</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.2893</v>
+        <v>0.5314</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1462</v>
+        <v>1.0388</v>
       </c>
       <c r="K18" t="n">
-        <v>1.0512</v>
+        <v>-0.2107</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.1974</v>
+        <v>1.2495</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4231</v>
+        <v>-1.0201</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3311</v>
+        <v>-0.302</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.092</v>
+        <v>-0.7181</v>
       </c>
       <c r="P18" t="n">
-        <v>1.0267</v>
+        <v>-1.0267</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0267</v>
+        <v>-3.0801</v>
       </c>
       <c r="R18" t="n">
         <v>2.0534</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2526</v>
+        <v>0.2915</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0272</v>
+        <v>-0.2287</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2798</v>
+        <v>0.5203</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.6591</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.6591</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. TAMAYO LESMES</t>
+          <t>P. GARCIA CARRERO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3828</v>
+        <v>-0.855</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1599</v>
+        <v>-1.3048</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.5427</v>
+        <v>0.4498</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.0947</v>
+        <v>-0.5693</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1264</v>
+        <v>0.72</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.2211</v>
+        <v>-1.2893</v>
       </c>
       <c r="J19" t="n">
-        <v>0.517</v>
+        <v>-0.1462</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6492</v>
+        <v>1.0512</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.1322</v>
+        <v>-1.1974</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.6117</v>
+        <v>-0.4231</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5228</v>
+        <v>-0.3311</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.089</v>
+        <v>-0.092</v>
       </c>
       <c r="P19" t="n">
-        <v>0.8214</v>
+        <v>1.0267</v>
       </c>
       <c r="Q19" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8481</v>
+        <v>2.0534</v>
       </c>
       <c r="S19" t="n">
-        <v>1.4881</v>
+        <v>0.3467</v>
       </c>
       <c r="T19" t="n">
-        <v>1.6696</v>
+        <v>-0.1318</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1815</v>
+        <v>0.4786</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.5975</v>
+        <v>-1.6591</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.5975</v>
+        <v>-1.6591</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5719</v>
+        <v>-1.0367</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.797</v>
+        <v>-0.274</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7749</v>
+        <v>-0.7627</v>
       </c>
       <c r="G20" t="n">
         <v>-2.3744</v>
@@ -2014,13 +2014,13 @@
         <v>0.616</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1865</v>
+        <v>0.7216</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3952</v>
+        <v>0.1278</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5817</v>
+        <v>0.5939</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. FABREGA URPINA</t>
+          <t>M. MUKENDI MUKENDI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7328</v>
+        <v>-1.8439</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.8977</v>
+        <v>-2.3711</v>
       </c>
       <c r="F21" t="n">
-        <v>1.1648</v>
+        <v>0.5271</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0187</v>
+        <v>-1.2853</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5127</v>
+        <v>-0.9538</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5314</v>
+        <v>-0.3314</v>
       </c>
       <c r="J21" t="n">
-        <v>1.0388</v>
+        <v>-0.6384</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.2107</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>1.2495</v>
+        <v>0.0395</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.0201</v>
+        <v>-0.6468</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.302</v>
+        <v>-0.2759</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.7181</v>
+        <v>-0.3709</v>
       </c>
       <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
         <v>-1.0267</v>
       </c>
-      <c r="Q21" t="n">
-        <v>-3.0801</v>
-      </c>
       <c r="R21" t="n">
-        <v>2.0534</v>
+        <v>1.0267</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7248</v>
+        <v>-0.1007</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8563</v>
+        <v>-0.4882</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1315</v>
+        <v>0.3875</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.4579</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.2177</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. MUKENDI MUKENDI</t>
+          <t>A. TAMAYO LESMES</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.0671</v>
+        <v>-2.3294</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.4757</v>
+        <v>-0.0953</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4086</v>
+        <v>-2.2341</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.2853</v>
+        <v>-1.0947</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.9538</v>
+        <v>0.1264</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.3314</v>
+        <v>-1.2211</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6384</v>
+        <v>0.517</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0.6492</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0395</v>
+        <v>-0.1322</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.6468</v>
+        <v>-1.6117</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2759</v>
+        <v>-0.5228</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.3709</v>
+        <v>-1.089</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>0.8214</v>
       </c>
       <c r="Q22" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R22" t="n">
-        <v>1.0267</v>
+        <v>1.8481</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3239</v>
+        <v>0.5414</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5928</v>
+        <v>0.4144</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2689</v>
+        <v>0.1271</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.4579</v>
+        <v>-2.5975</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.2177</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2402</v>
+        <v>-2.5975</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>13.9366</v>
+        <v>16.0287</v>
       </c>
       <c r="E23" t="n">
         <v>13.2942</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6422999999999999</v>
+        <v>2.7343</v>
       </c>
       <c r="G23" t="n">
         <v>11.2728</v>
@@ -2233,13 +2233,13 @@
         <v>-10.0168</v>
       </c>
       <c r="N23" t="n">
-        <v>-5.388299999999999</v>
+        <v>-5.3883</v>
       </c>
       <c r="O23" t="n">
         <v>-4.6288</v>
       </c>
       <c r="P23" t="n">
-        <v>7.186999999999999</v>
+        <v>7.187</v>
       </c>
       <c r="Q23" t="n">
         <v>-11.2937</v>
@@ -2248,13 +2248,13 @@
         <v>18.4808</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.6852</v>
+        <v>0.4065</v>
       </c>
       <c r="T23" t="n">
         <v>-1.919</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2337</v>
+        <v>2.326</v>
       </c>
       <c r="V23" t="n">
         <v>-2.8377</v>
